--- a/artfynd/S 2072-2022 artfynd.xlsx
+++ b/artfynd/S 2072-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ3"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -786,60 +786,52 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>103688262</v>
+        <v>136932528</v>
       </c>
       <c r="B3" t="n">
-        <v>99118</v>
+        <v>111666</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>219719</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Säfferot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Seseli libanotis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) W. D. J. Koch</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Mörtabergetd utsiktplats infart, Dlr</t>
+          <t>Skommarsveden, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>549704</v>
+        <v>549427</v>
       </c>
       <c r="R3" t="n">
-        <v>6706835</v>
+        <v>6706500</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -863,22 +855,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-09-21</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>17:00</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-09-21</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>17:00</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,25 +869,369 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136932528</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>136932529</v>
+      </c>
+      <c r="B4" t="n">
+        <v>111666</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>219719</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Säfferot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Seseli libanotis</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) W. D. J. Koch</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Skommarsveden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>549415</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6706446</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Stora Skedvi</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136932529</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>103688262</v>
+      </c>
+      <c r="B5" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Mörtabergetd utsiktplats infart, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>549704</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6706835</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Stora Skedvi</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2022-09-21</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2022-09-21</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
           <t>Eva-Liisa Eriksson Kukkonen</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AX5" t="inlineStr">
         <is>
           <t>Eva-Liisa Eriksson Kukkonen</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
-      <c r="AZ3" t="inlineStr">
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/103688262</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>136932527</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99273</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Skommarsveden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>549432</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6706513</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Stora Skedvi</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136932527</t>
         </is>
       </c>
     </row>
@@ -913,6 +1239,9 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 2072-2022 artfynd.xlsx
+++ b/artfynd/S 2072-2022 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136932528</v>
       </c>
       <c r="B3" t="n">
-        <v>111666</v>
+        <v>111672</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>136932529</v>
       </c>
       <c r="B4" t="n">
-        <v>111666</v>
+        <v>111672</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>136932527</v>
       </c>
       <c r="B6" t="n">
-        <v>99273</v>
+        <v>99279</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/S 2072-2022 artfynd.xlsx
+++ b/artfynd/S 2072-2022 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136932528</v>
       </c>
       <c r="B3" t="n">
-        <v>111672</v>
+        <v>111674</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>136932529</v>
       </c>
       <c r="B4" t="n">
-        <v>111672</v>
+        <v>111674</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>136932527</v>
       </c>
       <c r="B6" t="n">
-        <v>99279</v>
+        <v>99281</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/S 2072-2022 artfynd.xlsx
+++ b/artfynd/S 2072-2022 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136932528</v>
       </c>
       <c r="B3" t="n">
-        <v>111674</v>
+        <v>111675</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>136932529</v>
       </c>
       <c r="B4" t="n">
-        <v>111674</v>
+        <v>111675</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>136932527</v>
       </c>
       <c r="B6" t="n">
-        <v>99281</v>
+        <v>99282</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/S 2072-2022 artfynd.xlsx
+++ b/artfynd/S 2072-2022 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136932528</v>
       </c>
       <c r="B3" t="n">
-        <v>111675</v>
+        <v>111681</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>136932529</v>
       </c>
       <c r="B4" t="n">
-        <v>111675</v>
+        <v>111681</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>136932527</v>
       </c>
       <c r="B6" t="n">
-        <v>99282</v>
+        <v>99288</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/S 2072-2022 artfynd.xlsx
+++ b/artfynd/S 2072-2022 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136932528</v>
       </c>
       <c r="B3" t="n">
-        <v>111681</v>
+        <v>111685</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>136932529</v>
       </c>
       <c r="B4" t="n">
-        <v>111681</v>
+        <v>111685</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>136932527</v>
       </c>
       <c r="B6" t="n">
-        <v>99288</v>
+        <v>99292</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/S 2072-2022 artfynd.xlsx
+++ b/artfynd/S 2072-2022 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136932528</v>
       </c>
       <c r="B3" t="n">
-        <v>111685</v>
+        <v>111687</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>136932529</v>
       </c>
       <c r="B4" t="n">
-        <v>111685</v>
+        <v>111687</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>136932527</v>
       </c>
       <c r="B6" t="n">
-        <v>99292</v>
+        <v>99294</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/S 2072-2022 artfynd.xlsx
+++ b/artfynd/S 2072-2022 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136932528</v>
       </c>
       <c r="B3" t="n">
-        <v>111687</v>
+        <v>111689</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>136932529</v>
       </c>
       <c r="B4" t="n">
-        <v>111687</v>
+        <v>111689</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>136932527</v>
       </c>
       <c r="B6" t="n">
-        <v>99294</v>
+        <v>99296</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/S 2072-2022 artfynd.xlsx
+++ b/artfynd/S 2072-2022 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136932528</v>
       </c>
       <c r="B3" t="n">
-        <v>111689</v>
+        <v>111702</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>136932529</v>
       </c>
       <c r="B4" t="n">
-        <v>111689</v>
+        <v>111702</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>136932527</v>
       </c>
       <c r="B6" t="n">
-        <v>99296</v>
+        <v>99309</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/S 2072-2022 artfynd.xlsx
+++ b/artfynd/S 2072-2022 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136932528</v>
       </c>
       <c r="B3" t="n">
-        <v>111702</v>
+        <v>111704</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>136932529</v>
       </c>
       <c r="B4" t="n">
-        <v>111702</v>
+        <v>111704</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>136932527</v>
       </c>
       <c r="B6" t="n">
-        <v>99309</v>
+        <v>99311</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/S 2072-2022 artfynd.xlsx
+++ b/artfynd/S 2072-2022 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136932528</v>
       </c>
       <c r="B3" t="n">
-        <v>111704</v>
+        <v>111710</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>136932529</v>
       </c>
       <c r="B4" t="n">
-        <v>111704</v>
+        <v>111710</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>136932527</v>
       </c>
       <c r="B6" t="n">
-        <v>99311</v>
+        <v>99314</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/S 2072-2022 artfynd.xlsx
+++ b/artfynd/S 2072-2022 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136932528</v>
       </c>
       <c r="B3" t="n">
-        <v>111710</v>
+        <v>111732</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>136932529</v>
       </c>
       <c r="B4" t="n">
-        <v>111710</v>
+        <v>111732</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>136932527</v>
       </c>
       <c r="B6" t="n">
-        <v>99314</v>
+        <v>99324</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/S 2072-2022 artfynd.xlsx
+++ b/artfynd/S 2072-2022 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136932528</v>
       </c>
       <c r="B3" t="n">
-        <v>111732</v>
+        <v>111733</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>136932529</v>
       </c>
       <c r="B4" t="n">
-        <v>111732</v>
+        <v>111733</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>136932527</v>
       </c>
       <c r="B6" t="n">
-        <v>99324</v>
+        <v>99325</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/S 2072-2022 artfynd.xlsx
+++ b/artfynd/S 2072-2022 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136932528</v>
       </c>
       <c r="B3" t="n">
-        <v>111733</v>
+        <v>111738</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>136932529</v>
       </c>
       <c r="B4" t="n">
-        <v>111733</v>
+        <v>111738</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>136932527</v>
       </c>
       <c r="B6" t="n">
-        <v>99325</v>
+        <v>99330</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/S 2072-2022 artfynd.xlsx
+++ b/artfynd/S 2072-2022 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136932528</v>
       </c>
       <c r="B3" t="n">
-        <v>111738</v>
+        <v>111741</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>136932529</v>
       </c>
       <c r="B4" t="n">
-        <v>111738</v>
+        <v>111741</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>136932527</v>
       </c>
       <c r="B6" t="n">
-        <v>99330</v>
+        <v>99332</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/S 2072-2022 artfynd.xlsx
+++ b/artfynd/S 2072-2022 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136932528</v>
       </c>
       <c r="B3" t="n">
-        <v>111741</v>
+        <v>111747</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>136932529</v>
       </c>
       <c r="B4" t="n">
-        <v>111741</v>
+        <v>111747</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>136932527</v>
       </c>
       <c r="B6" t="n">
-        <v>99332</v>
+        <v>99338</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/S 2072-2022 artfynd.xlsx
+++ b/artfynd/S 2072-2022 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136932528</v>
       </c>
       <c r="B3" t="n">
-        <v>111747</v>
+        <v>111748</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>136932529</v>
       </c>
       <c r="B4" t="n">
-        <v>111747</v>
+        <v>111748</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/S 2072-2022 artfynd.xlsx
+++ b/artfynd/S 2072-2022 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136932528</v>
       </c>
       <c r="B3" t="n">
-        <v>111748</v>
+        <v>111760</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>136932529</v>
       </c>
       <c r="B4" t="n">
-        <v>111748</v>
+        <v>111760</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>136932527</v>
       </c>
       <c r="B6" t="n">
-        <v>99338</v>
+        <v>99350</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/S 2072-2022 artfynd.xlsx
+++ b/artfynd/S 2072-2022 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136932528</v>
       </c>
       <c r="B3" t="n">
-        <v>111760</v>
+        <v>111761</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>136932529</v>
       </c>
       <c r="B4" t="n">
-        <v>111760</v>
+        <v>111761</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>136932527</v>
       </c>
       <c r="B6" t="n">
-        <v>99350</v>
+        <v>99351</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/S 2072-2022 artfynd.xlsx
+++ b/artfynd/S 2072-2022 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136932528</v>
       </c>
       <c r="B3" t="n">
-        <v>111761</v>
+        <v>111764</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>136932529</v>
       </c>
       <c r="B4" t="n">
-        <v>111761</v>
+        <v>111764</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>136932527</v>
       </c>
       <c r="B6" t="n">
-        <v>99351</v>
+        <v>99354</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/S 2072-2022 artfynd.xlsx
+++ b/artfynd/S 2072-2022 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136932528</v>
       </c>
       <c r="B3" t="n">
-        <v>111764</v>
+        <v>111766</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>136932529</v>
       </c>
       <c r="B4" t="n">
-        <v>111764</v>
+        <v>111766</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>136932527</v>
       </c>
       <c r="B6" t="n">
-        <v>99354</v>
+        <v>99355</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/S 2072-2022 artfynd.xlsx
+++ b/artfynd/S 2072-2022 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136932528</v>
       </c>
       <c r="B3" t="n">
-        <v>111766</v>
+        <v>111770</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>136932529</v>
       </c>
       <c r="B4" t="n">
-        <v>111766</v>
+        <v>111770</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>136932527</v>
       </c>
       <c r="B6" t="n">
-        <v>99355</v>
+        <v>99358</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
